--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -33378,120 +33378,276 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUY TẮC</t>
+          <t xml:space="preserve">BƯỚC / QUY TẮC</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HƯỚNG DẪN</t>
+          <t xml:space="preserve">AI ĐỌC VÀ LÀM ĐÚNG NGAY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="23" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nguồn sự thật</t>
+          <t xml:space="preserve">0. Đọc nhanh</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan.json là hàng đợi; bảng Excel được tạo lại sau cập nhật G7</t>
+          <t xml:space="preserve">SOP: docs/TITLE-PLAN-1482-SOP.md; không quét lại toàn repo</t>
         </is>
       </c>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEO</t>
+          <t xml:space="preserve">1. Chọn 1–3 đề</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Không sản sinh thêm tiêu đề có cụm Thuê xe máy Hà Nội</t>
+          <t xml:space="preserve">Đọc plan.json hoặc chạy python scripts/title_plan_next.py --limit 3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danh mục</t>
+          <t xml:space="preserve">2. TP không là NT</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dùng Term ID cha con có thật; không tạo chuyên mục mới</t>
+          <t xml:space="preserve">TP-XXXX chỉ là đề tài; chưa Research PASS thì CHƯA được nhận Writer</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51 phường</t>
+          <t xml:space="preserve">3. So trùng</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giữ riêng chiến dịch 51 phường (Term 182) để không trùng</t>
+          <t xml:space="preserve">So URL, slug, intent với WordPress và data/topics.jsonl mới nhất</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nghiên cứu</t>
+          <t xml:space="preserve">4. Chọn danh mục</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tìm và đối chiếu 1-4 trang nguồn cho mỗi tiêu đề</t>
+          <t xml:space="preserve">Đúng Term ID và parent ở data/taxonomy.json; không tạo mục mới</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luật</t>
+          <t xml:space="preserve">5. Đọc nguồn</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bất kỳ khẳng định pháp luật nào đều cần nguồn chính thức</t>
+          <t xml:space="preserve">Tìm 1–4 URL HTTPS thật, ghi chứng cứ nguồn và thời điểm</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA</t>
+          <t xml:space="preserve">6. Chủ đề luật</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Writer và Publisher giữ QA &gt;=85; không thay đổi các cổng</t>
+          <t xml:space="preserve">GPLX/độ tuổi/luật phải tra nguồn nhà nước đang hiệu lực</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đã đăng</t>
+          <t xml:space="preserve">7. Giá/xe</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chỉ xác nhận khi ledger có phase VERIFIED và G7 PASS</t>
+          <t xml:space="preserve">NAP, giá, cọc theo data/business-facts.json; thông số theo hãng</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cũ</t>
+          <t xml:space="preserve">8. Research QA</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trước mỗi bài phải rà soát WP và kho chủ đề để chống trùng</t>
+          <t xml:space="preserve">Ứng viên qua Topic Factory/Research QA → NT-XXXXXX PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. W1–W9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim slot auto hợp lệ; không cướp lease hoặc nhận NT chưa PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="23" customHeight="1">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Viết bài</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.600–5.000 từ, intent riêng, 4+ H2, nguồn/internal link thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="23" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11. QA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEO ≥85 + Quality ≥85 + G1–G6 PASS mới đủ điều kiện Publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12. Publisher</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ Publisher được WordPress POST; đúng danh mục, chống trùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="23" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13. Xác minh G7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ G7 VERIFIED + PASS đầy đủ mới đánh dấu PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="23" customHeight="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. URL sạch</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slug theo tiêu đề; CẤM excel/xlsx/csv/tên file/TP-ID lọt vào URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15. SEO chính</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không tạo thêm nhiều bài trùng từ khóa thuê xe máy Hà Nội</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16. 51 phường</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giữ campaign phường ở Term 182 riêng, tránh nhân bản bài cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17. Mất mạng</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lưu TP/NT/session/slot/branch/commit/step; resume, không bắt đầu lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18. Nguồn sự thật</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excel để xem; plan.json để chọn; Topic Registry và G7 để kiểm trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19. Khi bị chặn</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REVIEW/HOLD/NEEDS_RECONCILE; không bịa QA hoặc POST lại mù</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20. Báo cáo</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TP-ID / NT-ID / QA / WordPress ID / URL công khai / lỗi thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LỆNH NGẮN AI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đọc SOP; lấy 3 TP; so trùng; nghiên cứu 1–4 nguồn; Research QA; Writer QA; G7</t>
         </is>
       </c>
     </row>

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -12705,9 +12705,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M188" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090681</t>
+        </is>
+      </c>
+      <c r="O188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4750</t>
+        </is>
+      </c>
+      <c r="P188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/lich-nghi-le-sap-toi-24-11-2026-nghi-1-ngay-tet-dinh-mui-4-10-2-2027-va-quoc-khanh-2-5-9-2027/</t>
+        </is>
+      </c>
+      <c r="Q188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:10:25.801532+00:00</t>
         </is>
       </c>
     </row>
@@ -33331,7 +33356,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33341,7 +33366,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -9355,9 +9355,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M138" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090631</t>
+        </is>
+      </c>
+      <c r="O138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4764</t>
+        </is>
+      </c>
+      <c r="P138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/giu-the-can-cuoc-khi-thue-xe-may-dieu-7-dieu-29-luat-can-cuoc-va-nghi-dinh-282-2025-noi-gi/</t>
+        </is>
+      </c>
+      <c r="Q138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T07:14:07.953143+00:00</t>
         </is>
       </c>
     </row>
@@ -17889,9 +17914,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M265" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090758</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4765</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/thue-xe-di-100-km-het-bao-nhieu-tien-xang-wave-alpha-vision-air-blade-theo-gia-15-10-2026/</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T07:14:07.953143+00:00</t>
         </is>
       </c>
     </row>
@@ -33356,7 +33406,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33366,7 +33416,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -6809,9 +6809,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M100" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090593</t>
+        </is>
+      </c>
+      <c r="O100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4767</t>
+        </is>
+      </c>
+      <c r="P100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/mang-xe-dap-len-tau-hoa-ky-gui-o-toa-hanh-ly-tinh-cuoc-50-kg-chiec-xe-dap-dien-100-kg-chiec/</t>
+        </is>
+      </c>
+      <c r="Q100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T07:27:53.401739+00:00</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33431,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33416,7 +33441,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -1918,9 +1918,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090520</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4772</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-buyt-ha-noi-chay-den-may-gio-tuyen-33-den-21h15-tuyen-54-den-21h00-tuyen-96-tuy-dau-ben/</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:42:50.565370+00:00</t>
         </is>
       </c>
     </row>
@@ -33431,7 +33456,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33441,7 +33466,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -7931,9 +7931,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M116" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090609</t>
+        </is>
+      </c>
+      <c r="O116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4774</t>
+        </is>
+      </c>
+      <c r="P116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xe-may-lien-tinh-qua-tram-bot-co-mat-phi-khong-thong-tu-32-2024-mien-tu-1-1-2025-tru-cao-toc/</t>
+        </is>
+      </c>
+      <c r="Q116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T09:58:19.998082+00:00</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33481,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33466,7 +33491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -712,9 +712,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090502</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4825</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/metro-ha-noi-khi-co-bao-tam-dung-tu-cap-8-thang-cuon-ngoai-troi-tat-buyt-co-the-ngung-tuyen/</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T11:47:12.687443+00:00</t>
         </is>
       </c>
     </row>
@@ -33481,7 +33506,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33491,7 +33516,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -17612,9 +17612,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M259" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090752</t>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4841</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bun-bo-hue-di-san-quoc-gia-ngay-27-6-2025-ho-so-ke-goc-tu-le-te-lang-va-ky-luc-300-to/</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T15:24:43.231174+00:00</t>
         </is>
       </c>
     </row>
@@ -33506,7 +33531,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33516,7 +33541,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -2437,9 +2437,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090527</t>
+        </is>
+      </c>
+      <c r="O34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4896</t>
+        </is>
+      </c>
+      <c r="P34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/day-nguon-bo-sac-xe-dien-son-thi-dung-tiep-duoc-khong-vinfast-bosch-va-shimano-dan-ngung-dung/</t>
+        </is>
+      </c>
+      <c r="Q34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -12922,9 +12947,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090682</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4897</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/metro-ha-noi-chay-den-22h00-22h30-hay-23h00-khi-buyt-da-nghi-trang-chinh-thuc-ghi-khac-nhau/</t>
+        </is>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -15401,9 +15451,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M226" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090719</t>
+        </is>
+      </c>
+      <c r="O226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4898</t>
+        </is>
+      </c>
+      <c r="P226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/tuyen-pho-thong-minh-o-pho-co-ha-noi-ma-qr-tren-bien-ten-pho-wi-fi-mien-phi-5-pho-thi-diem/</t>
+        </is>
+      </c>
+      <c r="Q226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T17:59:57.537437+00:00</t>
         </is>
       </c>
     </row>
@@ -33531,7 +33606,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33541,7 +33616,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-02-494.xlsx
@@ -377,9 +377,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-090497</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5021</t>
+        </is>
+      </c>
+      <c r="P4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/bang-o-to-hang-b-co-lai-duoc-xe-may-khong-dieu-57-luat-36-2024-va-thi-a1-duoc-mien-ly-thuyet/</t>
+        </is>
+      </c>
+      <c r="Q4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T20:40:31.742795+00:00</t>
         </is>
       </c>
     </row>
@@ -33606,7 +33631,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33616,7 +33641,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
